--- a/AAII_Financials/Yearly/BMRC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BMRC_YR_FIN.xlsx
@@ -3074,10 +3074,10 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>3424600</v>
+        <v>3422500</v>
       </c>
       <c r="E60" s="3">
-        <v>3226100</v>
+        <v>3223000</v>
       </c>
       <c r="F60" s="3">
         <v>3320200</v>
@@ -3176,10 +3176,10 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>16300</v>
+        <v>18400</v>
       </c>
       <c r="E62" s="3">
-        <v>13600</v>
+        <v>16600</v>
       </c>
       <c r="F62" s="3">
         <v>16900</v>
